--- a/data/trans_camb/P12_1_R-Edad-trans_camb.xlsx
+++ b/data/trans_camb/P12_1_R-Edad-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-4,81; 3,15</t>
+          <t>-4,83; 2,94</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-6,88; 0,82</t>
+          <t>-6,94; 0,79</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-9,17; 0,51</t>
+          <t>-9,35; 0,99</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,83; 6,24</t>
+          <t>-3,59; 6,95</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-10,35; -2,05</t>
+          <t>-10,18; -1,85</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-8,86; 3,85</t>
+          <t>-9,44; 3,5</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-2,86; 3,61</t>
+          <t>-2,75; 3,38</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-7,87; -1,89</t>
+          <t>-7,61; -1,94</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-8,3; -0,44</t>
+          <t>-7,83; 0,25</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-37,69; 38,31</t>
+          <t>-38,77; 32,46</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-55,36; 11,18</t>
+          <t>-56,06; 11,33</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-74,92; 14,56</t>
+          <t>-78,3; 12,73</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-21,28; 42,87</t>
+          <t>-20,34; 48,75</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-55,88; -13,65</t>
+          <t>-55,35; -12,83</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-49,11; 29,41</t>
+          <t>-52,3; 23,95</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-18,93; 28,6</t>
+          <t>-18,99; 28,3</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-52,16; -15,1</t>
+          <t>-50,87; -14,81</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-55,95; -2,62</t>
+          <t>-54,83; 0,81</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3,94; 3,27</t>
+          <t>-4,24; 2,9</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-8,82; -1,58</t>
+          <t>-8,2; -1,69</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-9,69; -0,32</t>
+          <t>-9,46; -0,98</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,71; 5,48</t>
+          <t>-3,68; 5,64</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-11,37; -3,34</t>
+          <t>-11,48; -3,18</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-14,33; -4,67</t>
+          <t>-14,04; -4,18</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-2,72; 3,11</t>
+          <t>-2,83; 3,0</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-8,63; -3,32</t>
+          <t>-8,57; -3,26</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-10,25; -3,82</t>
+          <t>-9,81; -3,56</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-25,52; 26,66</t>
+          <t>-26,62; 22,91</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-54,26; -11,88</t>
+          <t>-51,81; -12,94</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-61,96; -0,5</t>
+          <t>-60,44; -5,5</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-17,28; 31,63</t>
+          <t>-16,86; 32,69</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-52,81; -18,68</t>
+          <t>-53,53; -18,59</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-67,88; -27,26</t>
+          <t>-65,34; -23,29</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-15,22; 20,85</t>
+          <t>-15,88; 19,74</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-48,27; -21,79</t>
+          <t>-47,81; -21,53</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-58,53; -24,08</t>
+          <t>-56,35; -23,65</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-5,21; 3,63</t>
+          <t>-5,47; 3,01</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-12,51; -4,71</t>
+          <t>-12,69; -5,22</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-10,57; -2,23</t>
+          <t>-10,51; -2,4</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,69; 7,41</t>
+          <t>-2,36; 7,01</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-13,49; -5,82</t>
+          <t>-13,75; -5,72</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-9,46; -1,72</t>
+          <t>-9,86; -1,42</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-2,42; 3,76</t>
+          <t>-2,4; 3,93</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-12,15; -6,64</t>
+          <t>-12,18; -6,49</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-8,89; -3,22</t>
+          <t>-9,01; -3,18</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-26,29; 23,3</t>
+          <t>-27,16; 19,24</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-60,59; -29,19</t>
+          <t>-63,25; -31,78</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-53,3; -14,03</t>
+          <t>-52,67; -14,58</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-6,61; 37,49</t>
+          <t>-8,97; 35,36</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-56,46; -28,31</t>
+          <t>-56,32; -28,22</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-39,0; -8,57</t>
+          <t>-40,59; -6,09</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-11,42; 20,43</t>
+          <t>-11,04; 21,64</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-55,79; -36,12</t>
+          <t>-55,89; -35,24</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-40,88; -17,47</t>
+          <t>-42,0; -17,46</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-7,56; 1,95</t>
+          <t>-8,06; 1,51</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-8,18; 1,12</t>
+          <t>-8,32; 0,56</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-15,87; -1,63</t>
+          <t>-15,21; -1,65</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,86; 11,69</t>
+          <t>0,67; 11,22</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-11,94; -2,15</t>
+          <t>-11,75; -2,65</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-8,97; -0,24</t>
+          <t>-8,84; 0,39</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-1,66; 5,23</t>
+          <t>-1,97; 5,19</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-8,61; -2,12</t>
+          <t>-8,65; -1,95</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-13,16; -2,56</t>
+          <t>-12,81; -2,51</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-36,1; 12,14</t>
+          <t>-38,53; 11,46</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-39,47; 7,74</t>
+          <t>-39,47; 3,24</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-75,97; -9,51</t>
+          <t>-75,04; -9,58</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2,98; 56,41</t>
+          <t>2,7; 55,47</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-46,53; -10,07</t>
+          <t>-46,73; -13,03</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-34,9; -1,16</t>
+          <t>-34,67; 1,91</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-7,92; 28,03</t>
+          <t>-8,72; 28,58</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-39,37; -11,77</t>
+          <t>-38,06; -10,06</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-61,04; -13,46</t>
+          <t>-58,08; -12,69</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-7,1; 4,78</t>
+          <t>-6,38; 5,07</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-13,68; -2,82</t>
+          <t>-13,86; -3,79</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-8,78; 1,63</t>
+          <t>-8,4; 1,53</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-4,98; 7,67</t>
+          <t>-4,66; 7,89</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-11,57; 0,03</t>
+          <t>-11,46; 0,48</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-8,86; 1,61</t>
+          <t>-8,9; 1,24</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-4,0; 4,46</t>
+          <t>-3,77; 4,71</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-10,97; -2,66</t>
+          <t>-10,83; -3,12</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-6,79; 0,06</t>
+          <t>-7,28; -0,1</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-29,83; 25,8</t>
+          <t>-27,9; 26,46</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-55,04; -14,43</t>
+          <t>-57,21; -19,15</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-34,76; 8,91</t>
+          <t>-33,89; 8,84</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-16,54; 32,28</t>
+          <t>-15,7; 33,96</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-37,29; 0,49</t>
+          <t>-37,89; 1,43</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-29,19; 7,41</t>
+          <t>-28,94; 5,19</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-15,19; 20,68</t>
+          <t>-14,84; 21,73</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-42,44; -12,21</t>
+          <t>-41,44; -13,51</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-26,21; 0,43</t>
+          <t>-27,14; -0,18</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-8,28; 4,38</t>
+          <t>-7,7; 4,36</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-9,38; 2,46</t>
+          <t>-9,5; 1,98</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-7,81; 3,01</t>
+          <t>-7,59; 2,46</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-6,39; 7,28</t>
+          <t>-5,73; 7,67</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-12,62; 0,08</t>
+          <t>-12,32; -0,31</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-9,05; 50,95</t>
+          <t>-9,37; 51,39</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-5,28; 4,09</t>
+          <t>-5,45; 3,68</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-9,57; -1,16</t>
+          <t>-9,65; -1,49</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-6,08; 47,1</t>
+          <t>-6,24; 43,96</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-40,38; 30,45</t>
+          <t>-37,99; 29,04</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-45,32; 18,12</t>
+          <t>-44,97; 13,41</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-36,54; 21,06</t>
+          <t>-35,78; 16,13</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-20,01; 29,56</t>
+          <t>-18,44; 30,9</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-40,6; 0,57</t>
+          <t>-40,42; -1,13</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-31,03; 199,57</t>
+          <t>-32,13; 204,12</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-20,02; 19,38</t>
+          <t>-21,4; 17,72</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-37,58; -5,35</t>
+          <t>-38,28; -6,95</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-25,95; 213,08</t>
+          <t>-26,0; 206,07</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-10,22; 5,92</t>
+          <t>-11,29; 4,96</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-13,99; 0,83</t>
+          <t>-14,06; 0,54</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-11,27; 2,29</t>
+          <t>-10,98; 3,1</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3,26; 17,76</t>
+          <t>3,62; 17,8</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-4,94; 9,47</t>
+          <t>-3,96; 10,49</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-2,0; 9,59</t>
+          <t>-1,69; 10,56</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-0,05; 10,88</t>
+          <t>0,13; 11,07</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-6,62; 4,21</t>
+          <t>-6,56; 3,72</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-3,77; 5,36</t>
+          <t>-3,69; 5,04</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-35,34; 28,68</t>
+          <t>-38,01; 23,84</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-47,12; 3,85</t>
+          <t>-45,66; 4,27</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-37,53; 11,06</t>
+          <t>-36,97; 15,46</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>10,91; 82,17</t>
+          <t>12,31; 84,17</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-17,47; 42,89</t>
+          <t>-14,01; 50,08</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-6,06; 46,42</t>
+          <t>-5,83; 51,83</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-0,28; 47,29</t>
+          <t>0,41; 49,74</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-23,15; 18,88</t>
+          <t>-23,13; 16,74</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-13,14; 24,1</t>
+          <t>-13,12; 22,11</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-3,11; 0,61</t>
+          <t>-3,03; 0,74</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-7,14; -3,5</t>
+          <t>-7,05; -3,58</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-7,28; -2,44</t>
+          <t>-7,39; -2,42</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>1,42; 5,88</t>
+          <t>1,54; 5,6</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-7,71; -3,86</t>
+          <t>-7,58; -3,87</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-3,87; 15,33</t>
+          <t>-4,1; 16,55</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-0,08; 2,63</t>
+          <t>-0,13; 2,71</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-6,77; -4,24</t>
+          <t>-6,79; -4,21</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-4,67; 6,37</t>
+          <t>-4,6; 7,13</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-17,0; 3,99</t>
+          <t>-17,19; 4,68</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-40,02; -21,84</t>
+          <t>-39,67; -22,97</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-42,48; -15,11</t>
+          <t>-42,83; -15,18</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>5,97; 27,48</t>
+          <t>6,57; 25,85</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-32,82; -18,08</t>
+          <t>-32,31; -17,12</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-17,18; 68,27</t>
+          <t>-18,05; 74,73</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-0,34; 13,74</t>
+          <t>-0,68; 14,2</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-33,16; -22,08</t>
+          <t>-33,21; -21,98</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-23,43; 32,19</t>
+          <t>-23,09; 37,13</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P12_1_R-Edad-trans_camb.xlsx
+++ b/data/trans_camb/P12_1_R-Edad-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-4,83</t>
+          <t>-5,48</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-3,46</t>
+          <t>-3,27</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-4,5</t>
+          <t>-4,53</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-4,83; 2,94</t>
+          <t>-4,9; 3,53</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-6,94; 0,79</t>
+          <t>-7,46; 0,55</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-9,35; 0,99</t>
+          <t>-9,69; -0,33</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,59; 6,95</t>
+          <t>-4,11; 6,36</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-10,18; -1,85</t>
+          <t>-10,49; -1,5</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-9,44; 3,5</t>
+          <t>-9,12; 3,85</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-2,75; 3,38</t>
+          <t>-2,75; 3,77</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-7,61; -1,94</t>
+          <t>-7,8; -2,0</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-7,83; 0,25</t>
+          <t>-8,17; -0,44</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-45,09%</t>
+          <t>-51,11%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-21,0%</t>
+          <t>-19,81%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-33,29%</t>
+          <t>-33,47%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-38,77; 32,46</t>
+          <t>-38,19; 39,58</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-56,06; 11,33</t>
+          <t>-59,95; 6,4</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-78,3; 12,73</t>
+          <t>-77,74; 6,56</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-20,34; 48,75</t>
+          <t>-21,81; 45,72</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-55,35; -12,83</t>
+          <t>-56,54; -10,03</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-52,3; 23,95</t>
+          <t>-49,73; 29,15</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-18,99; 28,3</t>
+          <t>-19,22; 32,73</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-50,87; -14,81</t>
+          <t>-51,14; -15,6</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-54,83; 0,81</t>
+          <t>-56,27; -3,32</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-5,44</t>
+          <t>-4,46</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-8,96</t>
+          <t>-7,28</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-6,94</t>
+          <t>-5,65</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-4,24; 2,9</t>
+          <t>-4,18; 2,95</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-8,2; -1,69</t>
+          <t>-8,68; -1,34</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-9,46; -0,98</t>
+          <t>-8,72; 0,16</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,68; 5,64</t>
+          <t>-4,17; 4,84</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-11,48; -3,18</t>
+          <t>-11,38; -3,28</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-14,04; -4,18</t>
+          <t>-11,73; -2,51</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-2,83; 3,0</t>
+          <t>-2,96; 2,9</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-8,57; -3,26</t>
+          <t>-8,77; -3,34</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-9,81; -3,56</t>
+          <t>-8,56; -2,64</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-37,91%</t>
+          <t>-31,04%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-46,48%</t>
+          <t>-37,8%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-41,75%</t>
+          <t>-33,98%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-26,62; 22,91</t>
+          <t>-25,7; 22,77</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-51,81; -12,94</t>
+          <t>-53,87; -10,52</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-60,44; -5,5</t>
+          <t>-54,46; 3,06</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-16,86; 32,69</t>
+          <t>-19,54; 28,09</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-53,53; -18,59</t>
+          <t>-53,5; -19,26</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-65,34; -23,29</t>
+          <t>-55,03; -14,24</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-15,88; 19,74</t>
+          <t>-16,64; 18,88</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-47,81; -21,53</t>
+          <t>-49,13; -21,85</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-56,35; -23,65</t>
+          <t>-47,52; -16,64</t>
         </is>
       </c>
     </row>
@@ -1066,37 +1066,37 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
+          <t>-7,64</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>2,8</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>-9,7</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>-5,34</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>0,77</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>-9,31</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
           <t>-6,56</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>2,8</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-9,7</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>-5,49</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>0,77</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>-9,31</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>-6,09</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-5,47; 3,01</t>
+          <t>-5,62; 2,97</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-12,69; -5,22</t>
+          <t>-12,63; -4,83</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-10,51; -2,4</t>
+          <t>-11,64; -3,73</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,36; 7,01</t>
+          <t>-1,88; 7,61</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-13,75; -5,72</t>
+          <t>-13,96; -5,98</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-9,86; -1,42</t>
+          <t>-9,53; -1,22</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-2,4; 3,93</t>
+          <t>-2,3; 3,86</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-12,18; -6,49</t>
+          <t>-12,13; -6,53</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-9,01; -3,18</t>
+          <t>-9,55; -3,66</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-36,31%</t>
+          <t>-42,27%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-24,97%</t>
+          <t>-24,29%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-30,28%</t>
+          <t>-32,64%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-27,16; 19,24</t>
+          <t>-27,49; 18,97</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-63,25; -31,78</t>
+          <t>-62,78; -29,86</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-52,67; -14,58</t>
+          <t>-56,95; -22,19</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-8,97; 35,36</t>
+          <t>-7,99; 38,65</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-56,32; -28,22</t>
+          <t>-56,44; -29,05</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-40,59; -6,09</t>
+          <t>-39,37; -6,06</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-11,04; 21,64</t>
+          <t>-10,62; 21,0</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-55,89; -35,24</t>
+          <t>-55,91; -35,07</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-42,0; -17,46</t>
+          <t>-44,2; -20,19</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-7,49</t>
+          <t>-3,34</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-4,17</t>
+          <t>-3,15</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-6,26</t>
+          <t>-3,18</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-8,06; 1,51</t>
+          <t>-7,96; 1,56</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-8,32; 0,56</t>
+          <t>-8,09; 0,72</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-15,21; -1,65</t>
+          <t>-8,09; 0,42</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,67; 11,22</t>
+          <t>0,7; 11,53</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-11,75; -2,65</t>
+          <t>-11,81; -2,6</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-8,84; 0,39</t>
+          <t>-7,94; 0,64</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-1,97; 5,19</t>
+          <t>-2,23; 4,97</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-8,65; -1,95</t>
+          <t>-8,53; -2,06</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-12,81; -2,51</t>
+          <t>-6,36; -0,11</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-41,34%</t>
+          <t>-18,42%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-18,27%</t>
+          <t>-13,82%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-30,59%</t>
+          <t>-15,52%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-38,53; 11,46</t>
+          <t>-37,81; 10,16</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-39,47; 3,24</t>
+          <t>-39,33; 3,87</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-75,04; -9,58</t>
+          <t>-37,89; 3,21</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2,7; 55,47</t>
+          <t>2,69; 57,82</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-46,73; -13,03</t>
+          <t>-46,13; -11,92</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-34,67; 1,91</t>
+          <t>-31,04; 3,19</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-8,72; 28,58</t>
+          <t>-9,65; 27,06</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-38,06; -10,06</t>
+          <t>-38,49; -11,2</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-58,08; -12,69</t>
+          <t>-28,36; -0,67</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>-3,03</t>
+          <t>-3,21</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-3,57</t>
+          <t>-3,59</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-3,39</t>
+          <t>-3,46</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-6,38; 5,07</t>
+          <t>-7,1; 4,35</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-13,86; -3,79</t>
+          <t>-13,68; -3,78</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-8,4; 1,53</t>
+          <t>-8,48; 1,41</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-4,66; 7,89</t>
+          <t>-4,47; 8,08</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-11,46; 0,48</t>
+          <t>-11,22; 0,33</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-8,9; 1,24</t>
+          <t>-8,04; 1,9</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-3,77; 4,71</t>
+          <t>-3,75; 4,41</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-10,83; -3,12</t>
+          <t>-11,2; -3,18</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-7,28; -0,1</t>
+          <t>-7,11; 0,14</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>-14,39%</t>
+          <t>-15,23%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-13,31%</t>
+          <t>-13,39%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-14,14%</t>
+          <t>-14,43%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-27,9; 26,46</t>
+          <t>-30,03; 23,5</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-57,21; -19,15</t>
+          <t>-57,75; -20,21</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-33,89; 8,84</t>
+          <t>-35,33; 7,92</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-15,7; 33,96</t>
+          <t>-14,79; 35,2</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-37,89; 1,43</t>
+          <t>-37,02; 1,2</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-28,94; 5,19</t>
+          <t>-26,88; 8,46</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-14,84; 21,73</t>
+          <t>-14,47; 20,18</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-41,44; -13,51</t>
+          <t>-42,8; -14,24</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-27,14; -0,18</t>
+          <t>-26,52; 1,08</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>-2,24</t>
+          <t>-2,54</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>19,65</t>
+          <t>-7,0</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>12,25</t>
+          <t>-5,07</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-7,7; 4,36</t>
+          <t>-8,44; 3,95</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-9,5; 1,98</t>
+          <t>-9,74; 2,01</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-7,59; 2,46</t>
+          <t>-8,0; 2,09</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-5,73; 7,67</t>
+          <t>-5,42; 7,27</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-12,32; -0,31</t>
+          <t>-12,52; 0,2</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-9,37; 51,39</t>
+          <t>-13,19; -2,15</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-5,45; 3,68</t>
+          <t>-5,4; 4,07</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-9,65; -1,49</t>
+          <t>-9,58; -0,76</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-6,24; 43,96</t>
+          <t>-8,79; -1,16</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>-12,64%</t>
+          <t>-14,34%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>70,48%</t>
+          <t>-25,13%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>52,8%</t>
+          <t>-21,84%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-37,99; 29,04</t>
+          <t>-39,89; 28,32</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-44,97; 13,41</t>
+          <t>-45,49; 13,68</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-35,78; 16,13</t>
+          <t>-37,39; 15,16</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-18,44; 30,9</t>
+          <t>-17,76; 30,29</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-40,42; -1,13</t>
+          <t>-39,97; 1,12</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-32,13; 204,12</t>
+          <t>-40,58; -8,52</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-21,4; 17,72</t>
+          <t>-20,95; 19,39</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-38,28; -6,95</t>
+          <t>-38,2; -3,61</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-26,0; 206,07</t>
+          <t>-35,29; -6,35</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>-4,34</t>
+          <t>-4,53</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>4,19</t>
+          <t>4,27</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>0,78</t>
+          <t>0,74</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-11,29; 4,96</t>
+          <t>-10,18; 5,44</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-14,06; 0,54</t>
+          <t>-14,09; 0,36</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-10,98; 3,1</t>
+          <t>-11,21; 1,75</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3,62; 17,8</t>
+          <t>3,23; 17,38</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-3,96; 10,49</t>
+          <t>-4,46; 10,07</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-1,69; 10,56</t>
+          <t>-1,52; 9,42</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>0,13; 11,07</t>
+          <t>-0,16; 10,67</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-6,56; 3,72</t>
+          <t>-6,2; 4,15</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-3,69; 5,04</t>
+          <t>-3,45; 5,63</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>-17,08%</t>
+          <t>-17,82%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>16,42%</t>
+          <t>16,74%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>2,92%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-38,01; 23,84</t>
+          <t>-35,05; 25,95</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-45,66; 4,27</t>
+          <t>-46,97; 2,16</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-36,97; 15,46</t>
+          <t>-37,35; 8,71</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>12,31; 84,17</t>
+          <t>10,67; 79,83</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-14,01; 50,08</t>
+          <t>-15,27; 47,19</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-5,83; 51,83</t>
+          <t>-5,05; 42,38</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>0,41; 49,74</t>
+          <t>-0,46; 47,43</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-23,13; 16,74</t>
+          <t>-22,05; 18,78</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-13,12; 22,11</t>
+          <t>-12,13; 25,86</t>
         </is>
       </c>
     </row>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>-4,35</t>
+          <t>-3,56</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>1,08</t>
+          <t>-2,89</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>-1,53</t>
+          <t>-3,18</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-3,03; 0,74</t>
+          <t>-2,94; 0,83</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-7,05; -3,58</t>
+          <t>-6,95; -3,41</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-7,39; -2,42</t>
+          <t>-5,22; -1,69</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>1,54; 5,6</t>
+          <t>1,65; 5,94</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-7,58; -3,87</t>
+          <t>-7,73; -3,91</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-4,1; 16,55</t>
+          <t>-4,91; -1,04</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-0,13; 2,71</t>
+          <t>-0,11; 2,69</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-6,79; -4,21</t>
+          <t>-6,75; -4,21</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-4,6; 7,13</t>
+          <t>-4,53; -1,92</t>
         </is>
       </c>
     </row>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>-25,71%</t>
+          <t>-21,04%</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>-12,91%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>-7,75%</t>
+          <t>-16,16%</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-17,19; 4,68</t>
+          <t>-16,69; 4,84</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-39,67; -22,97</t>
+          <t>-38,7; -21,26</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-42,83; -15,18</t>
+          <t>-29,44; -10,59</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>6,57; 25,85</t>
+          <t>7,11; 27,76</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-32,31; -17,12</t>
+          <t>-33,12; -18,32</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-18,05; 74,73</t>
+          <t>-20,72; -4,9</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-0,68; 14,2</t>
+          <t>-0,55; 14,05</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-33,21; -21,98</t>
+          <t>-33,27; -22,0</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-23,09; 37,13</t>
+          <t>-22,08; -10,02</t>
         </is>
       </c>
     </row>
